--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N48_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.570366646985712</v>
+        <v>0.7426845801351782</v>
       </c>
       <c r="D2" t="n">
-        <v>3.64080132574586</v>
+        <v>0.5916302154337022</v>
       </c>
       <c r="E2" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F2" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.52166270208078</v>
+        <v>3.984770189088127</v>
       </c>
       <c r="D3" t="n">
-        <v>24.68485698417809</v>
+        <v>4.011289259928939</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F3" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.44843672462637</v>
+        <v>4.785370967751786</v>
       </c>
       <c r="D4" t="n">
-        <v>29.23830702069862</v>
+        <v>4.751224890863526</v>
       </c>
       <c r="E4" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F4" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>33.39072472930471</v>
+        <v>5.425992768512015</v>
       </c>
       <c r="D5" t="n">
-        <v>24.48166929601154</v>
+        <v>3.978271260601876</v>
       </c>
       <c r="E5" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F5" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.92835334037908</v>
+        <v>6.3258574178116</v>
       </c>
       <c r="D6" t="n">
-        <v>32.80243893371345</v>
+        <v>5.330396326728437</v>
       </c>
       <c r="E6" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F6" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.36383256092675</v>
+        <v>6.071622791150596</v>
       </c>
       <c r="D7" t="n">
-        <v>37.58039974736698</v>
+        <v>6.106814958947135</v>
       </c>
       <c r="E7" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F7" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.46739707128715</v>
+        <v>5.763452024084162</v>
       </c>
       <c r="D8" t="n">
-        <v>34.98847742857286</v>
+        <v>5.68562758214309</v>
       </c>
       <c r="E8" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F8" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.70184040149178</v>
+        <v>4.664049065242414</v>
       </c>
       <c r="D9" t="n">
-        <v>28.96835493388922</v>
+        <v>4.707357676756998</v>
       </c>
       <c r="E9" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F9" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.39513783983641</v>
+        <v>6.889209898973417</v>
       </c>
       <c r="D10" t="n">
-        <v>42.36925225381268</v>
+        <v>6.88500349124456</v>
       </c>
       <c r="E10" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F10" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>54.82971883313221</v>
+        <v>8.909829310383985</v>
       </c>
       <c r="D11" t="n">
-        <v>54.69278043699386</v>
+        <v>8.887576821011503</v>
       </c>
       <c r="E11" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F11" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>46.0403247680379</v>
+        <v>7.481552774806159</v>
       </c>
       <c r="D12" t="n">
-        <v>45.7750948684307</v>
+        <v>7.438452916119989</v>
       </c>
       <c r="E12" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F12" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.64824313200063</v>
+        <v>6.280339508950102</v>
       </c>
       <c r="D13" t="n">
-        <v>38.84607735889191</v>
+        <v>6.312487570819936</v>
       </c>
       <c r="E13" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F13" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>53.29429827536972</v>
+        <v>8.660323469747579</v>
       </c>
       <c r="D14" t="n">
-        <v>53.05326562874646</v>
+        <v>8.621155664671299</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F14" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>31.95398422565498</v>
+        <v>5.192522436668935</v>
       </c>
       <c r="D15" t="n">
-        <v>32.31463167521192</v>
+        <v>5.251127647221938</v>
       </c>
       <c r="E15" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F15" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>24.67810320246396</v>
+        <v>4.010191770400394</v>
       </c>
       <c r="D16" t="n">
-        <v>25.03658836971507</v>
+        <v>4.068445610078699</v>
       </c>
       <c r="E16" t="n">
-        <v>12.0101035170689</v>
+        <v>1.951641821523696</v>
       </c>
       <c r="F16" t="n">
-        <v>12.29824023768534</v>
+        <v>1.998464038623868</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
